--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2597-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2597-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DB0E3E4-CCD0-4108-9B9B-FF8EA9A03F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A3D11C4-8DAC-40CF-8C40-2A6C8E1181A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{48A51D3D-D9BE-4E8F-8219-3988000CD9D2}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{322CE4F7-5382-40CA-8828-1E4B218C5D9C}"/>
   </bookViews>
   <sheets>
     <sheet name="2597-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1547,24 +1547,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C790258D-47A1-4200-B413-E717847871E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F97DB048-1467-42E4-9BDF-BC3069644660}">
   <dimension ref="A1:X26"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1598,7 +1597,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1634,7 +1633,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1686,7 +1685,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1754,7 +1753,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2024</v>
       </c>
@@ -1826,7 +1825,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="13" t="s">
@@ -1854,7 +1853,7 @@
       <c r="W6" s="48"/>
       <c r="X6" s="44"/>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="49">
         <v>2023</v>
       </c>
@@ -1926,7 +1925,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="51"/>
       <c r="B8" s="52"/>
       <c r="C8" s="16" t="s">
@@ -1954,7 +1953,7 @@
       <c r="W8" s="58"/>
       <c r="X8" s="54"/>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="59">
         <v>2022</v>
       </c>
@@ -2026,7 +2025,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="61">
         <v>2021</v>
       </c>
@@ -2098,7 +2097,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <v>2020</v>
       </c>
@@ -2170,7 +2169,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="41"/>
       <c r="B12" s="42"/>
       <c r="C12" s="13" t="s">
@@ -2198,7 +2197,7 @@
       <c r="W12" s="48"/>
       <c r="X12" s="44"/>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="61">
         <v>2019</v>
       </c>
@@ -2270,7 +2269,7 @@
         <v>9.59</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="59">
         <v>2018</v>
       </c>
@@ -2342,7 +2341,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="61">
         <v>2017</v>
       </c>
@@ -2414,7 +2413,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="59">
         <v>2016</v>
       </c>
@@ -2486,7 +2485,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="61">
         <v>2015</v>
       </c>
@@ -2558,7 +2557,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="59">
         <v>2014</v>
       </c>
@@ -2630,7 +2629,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="61">
         <v>2013</v>
       </c>
@@ -2702,7 +2701,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="59">
         <v>2012</v>
       </c>
@@ -2774,7 +2773,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="61">
         <v>2011</v>
       </c>
@@ -2846,7 +2845,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="59">
         <v>2010</v>
       </c>
@@ -2918,7 +2917,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="61">
         <v>2009</v>
       </c>
@@ -2990,7 +2989,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="59">
         <v>2008</v>
       </c>
@@ -3062,7 +3061,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="61">
         <v>2007</v>
       </c>
@@ -3134,7 +3133,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="59" t="s">
         <v>49</v>
       </c>
